--- a/public/sap-reporting/expansion-150-downloads/EXT-SD06-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD06-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R47f47dc2ace64aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R8baaaa726f1b4ee7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb37f1f45878f4a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R89f5ba48260344ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf752bf513202438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R602d7afc18464ec7"/>
   </x:sheets>
 </x:workbook>
 </file>
